--- a/notebooks/Random Forest/predictions_afr.xlsx
+++ b/notebooks/Random Forest/predictions_afr.xlsx
@@ -479,7 +479,7 @@
         <v>1.49</v>
       </c>
       <c r="D3" t="n">
-        <v>1.462482141955267</v>
+        <v>1.462482141955268</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>1.459</v>
       </c>
       <c r="D4" t="n">
-        <v>1.465613336399712</v>
+        <v>1.465613336399713</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>1.635</v>
       </c>
       <c r="D5" t="n">
-        <v>1.596931855158731</v>
+        <v>1.59693185515873</v>
       </c>
     </row>
     <row r="6">
@@ -575,7 +575,7 @@
         <v>1.119</v>
       </c>
       <c r="D9" t="n">
-        <v>1.062724353174602</v>
+        <v>1.062724353174603</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>1.346</v>
       </c>
       <c r="D14" t="n">
-        <v>1.350658155522109</v>
+        <v>1.35065815552211</v>
       </c>
     </row>
     <row r="15">
@@ -719,7 +719,7 @@
         <v>1.339</v>
       </c>
       <c r="D18" t="n">
-        <v>1.297026954004329</v>
+        <v>1.297026954004328</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>1.666</v>
       </c>
       <c r="D19" t="n">
-        <v>1.640994842352092</v>
+        <v>1.640994842352093</v>
       </c>
     </row>
     <row r="20">
@@ -863,7 +863,7 @@
         <v>1.262</v>
       </c>
       <c r="D27" t="n">
-        <v>1.244065982572983</v>
+        <v>1.244065982572982</v>
       </c>
     </row>
     <row r="28">
@@ -943,7 +943,7 @@
         <v>1.451</v>
       </c>
       <c r="D32" t="n">
-        <v>1.436864606962482</v>
+        <v>1.436864606962483</v>
       </c>
     </row>
     <row r="33">
@@ -991,7 +991,7 @@
         <v>1.257</v>
       </c>
       <c r="D35" t="n">
-        <v>1.257693105769232</v>
+        <v>1.257693105769231</v>
       </c>
     </row>
     <row r="36">
@@ -1071,7 +1071,7 @@
         <v>1.198</v>
       </c>
       <c r="D40" t="n">
-        <v>1.109357892857142</v>
+        <v>1.109357892857143</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         <v>1.527</v>
       </c>
       <c r="D41" t="n">
-        <v>1.538278867560802</v>
+        <v>1.538278867560801</v>
       </c>
     </row>
     <row r="42">
@@ -1135,7 +1135,7 @@
         <v>1.346</v>
       </c>
       <c r="D44" t="n">
-        <v>1.294233996392496</v>
+        <v>1.294233996392495</v>
       </c>
     </row>
     <row r="45">
@@ -1167,7 +1167,7 @@
         <v>1.414</v>
       </c>
       <c r="D46" t="n">
-        <v>1.381564125595359</v>
+        <v>1.381564125595358</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         <v>1.597</v>
       </c>
       <c r="D47" t="n">
-        <v>1.634954904761905</v>
+        <v>1.634954904761904</v>
       </c>
     </row>
     <row r="48">
@@ -1263,7 +1263,7 @@
         <v>1.564</v>
       </c>
       <c r="D52" t="n">
-        <v>1.540493440222303</v>
+        <v>1.540493440222304</v>
       </c>
     </row>
     <row r="53">
@@ -1311,7 +1311,7 @@
         <v>1.047</v>
       </c>
       <c r="D55" t="n">
-        <v>1.062222490079365</v>
+        <v>1.062222490079364</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         <v>1.619</v>
       </c>
       <c r="D56" t="n">
-        <v>1.656104008151796</v>
+        <v>1.656104008151795</v>
       </c>
     </row>
     <row r="57">
@@ -1423,7 +1423,7 @@
         <v>1.104</v>
       </c>
       <c r="D62" t="n">
-        <v>1.068045865079364</v>
+        <v>1.068045865079365</v>
       </c>
     </row>
     <row r="63">
@@ -1583,7 +1583,7 @@
         <v>1.179</v>
       </c>
       <c r="D72" t="n">
-        <v>1.087110261904761</v>
+        <v>1.087110261904762</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         <v>1.72</v>
       </c>
       <c r="D73" t="n">
-        <v>1.70771970436536</v>
+        <v>1.707719704365359</v>
       </c>
     </row>
     <row r="74">
@@ -1631,7 +1631,7 @@
         <v>1.34</v>
       </c>
       <c r="D75" t="n">
-        <v>1.296922121031746</v>
+        <v>1.296922121031745</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         <v>1.463</v>
       </c>
       <c r="D76" t="n">
-        <v>1.472994753066378</v>
+        <v>1.472994753066379</v>
       </c>
     </row>
     <row r="77">
@@ -1679,7 +1679,7 @@
         <v>1.471</v>
       </c>
       <c r="D78" t="n">
-        <v>1.441832563492063</v>
+        <v>1.441832563492064</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         <v>2.66</v>
       </c>
       <c r="D79" t="n">
-        <v>2.649130948232322</v>
+        <v>2.649130948232323</v>
       </c>
     </row>
     <row r="80">
@@ -1743,7 +1743,7 @@
         <v>1.946</v>
       </c>
       <c r="D82" t="n">
-        <v>1.909437232683984</v>
+        <v>1.909437232683983</v>
       </c>
     </row>
     <row r="83">

--- a/notebooks/Random Forest/predictions_afr.xlsx
+++ b/notebooks/Random Forest/predictions_afr.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР</t>
+          <t>СКР_прогноз</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>predictions</t>
+          <t>СКР_реальный</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_абсолютная</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_относительная_%</t>
         </is>
       </c>
     </row>
@@ -457,13 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="n">
+        <v>1.34630715316341</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.305</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.291373049603175</v>
+      <c r="E2" t="n">
+        <v>-0.04130715316340994</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.165299092981604</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="n">
+        <v>1.441225350164975</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.49</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.462482141955268</v>
+      <c r="E3" t="n">
+        <v>0.04877464983502477</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.273466431880857</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="n">
+        <v>1.476763364048759</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.459</v>
       </c>
-      <c r="D4" t="n">
-        <v>1.465613336399713</v>
+      <c r="E4" t="n">
+        <v>-0.01776336404875845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.217502676405651</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="n">
+        <v>1.605448160998002</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.635</v>
       </c>
-      <c r="D5" t="n">
-        <v>1.59693185515873</v>
+      <c r="E5" t="n">
+        <v>0.02955183900199754</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.807451926727678</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="n">
+        <v>1.184308950408526</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.123</v>
       </c>
-      <c r="D6" t="n">
-        <v>1.080854416666666</v>
+      <c r="E6" t="n">
+        <v>-0.0613089504085258</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-5.459390063092235</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="n">
+        <v>1.212789692300893</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.19</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.119958041666666</v>
+      <c r="E7" t="n">
+        <v>-0.02278969230089345</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.915100193352391</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="n">
+        <v>1.159599515172466</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.147</v>
       </c>
-      <c r="D8" t="n">
-        <v>1.088572369047619</v>
+      <c r="E8" t="n">
+        <v>-0.01259951517246627</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.098475603528009</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="n">
+        <v>1.153522449314574</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.119</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.062724353174603</v>
+      <c r="E9" t="n">
+        <v>-0.03452244931457416</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.085116113902963</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="n">
+        <v>1.374991444656341</v>
+      </c>
+      <c r="D10" t="n">
         <v>1.391</v>
       </c>
-      <c r="D10" t="n">
-        <v>1.382215025656695</v>
+      <c r="E10" t="n">
+        <v>0.01600855534365864</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.15086666740896</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="n">
+        <v>1.221534288064292</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.222</v>
       </c>
-      <c r="D11" t="n">
-        <v>1.195543341089466</v>
+      <c r="E11" t="n">
+        <v>0.0004657119357081019</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03811063303666955</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="n">
+        <v>1.601996003553828</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.559</v>
       </c>
-      <c r="D12" t="n">
-        <v>1.571706666056166</v>
+      <c r="E12" t="n">
+        <v>-0.04299600355382771</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-2.75792197266374</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="n">
+        <v>1.609771294701715</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.548</v>
       </c>
-      <c r="D13" t="n">
-        <v>1.567724700563326</v>
+      <c r="E13" t="n">
+        <v>-0.06177129470171505</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-3.990393714581075</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="n">
+        <v>1.354218973423504</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.346</v>
       </c>
-      <c r="D14" t="n">
-        <v>1.35065815552211</v>
+      <c r="E14" t="n">
+        <v>-0.008218973423503417</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.6106220968427502</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="n">
+        <v>1.665483957135447</v>
+      </c>
+      <c r="D15" t="n">
         <v>1.65</v>
       </c>
-      <c r="D15" t="n">
-        <v>1.661114880615931</v>
+      <c r="E15" t="n">
+        <v>-0.01548395713544704</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.9384216445725476</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="n">
+        <v>1.522749674501962</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.526</v>
       </c>
-      <c r="D16" t="n">
-        <v>1.517964771915585</v>
+      <c r="E16" t="n">
+        <v>0.00325032549803761</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2129964284428315</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="n">
+        <v>1.289072622232511</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.183</v>
       </c>
-      <c r="D17" t="n">
-        <v>1.184007073232322</v>
+      <c r="E17" t="n">
+        <v>-0.1060726222325112</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-8.966409318048287</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C18" t="n">
+        <v>1.316430579274658</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.339</v>
       </c>
-      <c r="D18" t="n">
-        <v>1.297026954004328</v>
+      <c r="E18" t="n">
+        <v>0.02256942072534174</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.685542996664805</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="n">
+        <v>1.601448499936831</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.666</v>
       </c>
-      <c r="D19" t="n">
-        <v>1.640994842352093</v>
+      <c r="E19" t="n">
+        <v>0.06455150006316868</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.874639859734014</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C20" t="n">
+        <v>1.331868448128098</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.34</v>
       </c>
-      <c r="D20" t="n">
-        <v>1.290985803932179</v>
+      <c r="E20" t="n">
+        <v>0.008131551871902065</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6068322292464228</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C21" t="n">
+        <v>1.258952174454539</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.221</v>
       </c>
-      <c r="D21" t="n">
-        <v>1.235658057789433</v>
+      <c r="E21" t="n">
+        <v>-0.03795217445453924</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3.10828619611296</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C22" t="n">
+        <v>1.48281620002669</v>
+      </c>
+      <c r="D22" t="n">
         <v>1.473</v>
       </c>
-      <c r="D22" t="n">
-        <v>1.486780000319126</v>
+      <c r="E22" t="n">
+        <v>-0.009816200026689925</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.6664086915607552</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C23" t="n">
+        <v>1.493659907526216</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.552</v>
       </c>
-      <c r="D23" t="n">
-        <v>1.533591108111917</v>
+      <c r="E23" t="n">
+        <v>0.05834009247378402</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.759026576919074</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C24" t="n">
+        <v>1.503597848628165</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.532</v>
       </c>
-      <c r="D24" t="n">
-        <v>1.519202301046177</v>
+      <c r="E24" t="n">
+        <v>0.0284021513718351</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.85392632975425</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C25" t="n">
+        <v>1.407142333699811</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.436</v>
       </c>
-      <c r="D25" t="n">
-        <v>1.387749219131208</v>
+      <c r="E25" t="n">
+        <v>0.02885766630018871</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.009586789706735</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C26" t="n">
+        <v>1.649311918951633</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.642</v>
       </c>
-      <c r="D26" t="n">
-        <v>1.642318459776335</v>
+      <c r="E26" t="n">
+        <v>-0.007311918951633523</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.4453056608790208</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C27" t="n">
+        <v>1.269275929643216</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.262</v>
       </c>
-      <c r="D27" t="n">
-        <v>1.244065982572982</v>
+      <c r="E27" t="n">
+        <v>-0.007275929643215662</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.5765395913800049</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C28" t="n">
+        <v>1.08756169011544</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.88</v>
       </c>
-      <c r="D28" t="n">
-        <v>1.040313490079365</v>
+      <c r="E28" t="n">
+        <v>-0.2075616901154399</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-23.58655569493635</v>
       </c>
     </row>
     <row r="29">
@@ -889,13 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C29" t="n">
+        <v>1.202585417513789</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.233</v>
       </c>
-      <c r="D29" t="n">
-        <v>1.178556906565656</v>
+      <c r="E29" t="n">
+        <v>0.03041458248621121</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.466713908046326</v>
       </c>
     </row>
     <row r="30">
@@ -905,13 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>1.410770034180244</v>
+      </c>
+      <c r="D30" t="n">
         <v>1.34</v>
       </c>
-      <c r="D30" t="n">
-        <v>1.395657796536796</v>
+      <c r="E30" t="n">
+        <v>-0.07077003418024419</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-5.281345834346581</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +1105,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C31" t="n">
+        <v>1.304646471560846</v>
+      </c>
+      <c r="D31" t="n">
         <v>1.352</v>
       </c>
-      <c r="D31" t="n">
-        <v>1.300498767857143</v>
+      <c r="E31" t="n">
+        <v>0.04735352843915375</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.502479914138591</v>
       </c>
     </row>
     <row r="32">
@@ -937,13 +1127,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C32" t="n">
+        <v>1.442985546997392</v>
+      </c>
+      <c r="D32" t="n">
         <v>1.451</v>
       </c>
-      <c r="D32" t="n">
-        <v>1.436864606962483</v>
+      <c r="E32" t="n">
+        <v>0.008014453002607835</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5523399726125316</v>
       </c>
     </row>
     <row r="33">
@@ -953,13 +1149,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C33" t="n">
+        <v>1.863609791125542</v>
+      </c>
+      <c r="D33" t="n">
         <v>1.913</v>
       </c>
-      <c r="D33" t="n">
-        <v>1.832843726190477</v>
+      <c r="E33" t="n">
+        <v>0.04939020887445777</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.58181959615566</v>
       </c>
     </row>
     <row r="34">
@@ -969,13 +1171,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C34" t="n">
+        <v>1.291393543935119</v>
+      </c>
+      <c r="D34" t="n">
         <v>1.309</v>
       </c>
-      <c r="D34" t="n">
-        <v>1.267765405192031</v>
+      <c r="E34" t="n">
+        <v>0.0176064560648812</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.345031020999328</v>
       </c>
     </row>
     <row r="35">
@@ -985,13 +1193,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C35" t="n">
+        <v>1.300061124096299</v>
+      </c>
+      <c r="D35" t="n">
         <v>1.257</v>
       </c>
-      <c r="D35" t="n">
-        <v>1.257693105769231</v>
+      <c r="E35" t="n">
+        <v>-0.04306112409629881</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-3.425705974248115</v>
       </c>
     </row>
     <row r="36">
@@ -1001,13 +1215,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C36" t="n">
+        <v>1.485267188353305</v>
+      </c>
+      <c r="D36" t="n">
         <v>1.492</v>
       </c>
-      <c r="D36" t="n">
-        <v>1.487244880550006</v>
+      <c r="E36" t="n">
+        <v>0.006732811646695147</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4512608342288973</v>
       </c>
     </row>
     <row r="37">
@@ -1017,13 +1237,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C37" t="n">
+        <v>1.497830622332682</v>
+      </c>
+      <c r="D37" t="n">
         <v>1.495</v>
       </c>
-      <c r="D37" t="n">
-        <v>1.498106623515373</v>
+      <c r="E37" t="n">
+        <v>-0.002830622332682386</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.1893392864670493</v>
       </c>
     </row>
     <row r="38">
@@ -1033,13 +1259,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C38" t="n">
+        <v>1.459560244360044</v>
+      </c>
+      <c r="D38" t="n">
         <v>1.502</v>
       </c>
-      <c r="D38" t="n">
-        <v>1.459610278860029</v>
+      <c r="E38" t="n">
+        <v>0.0424397556399565</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.825549643139581</v>
       </c>
     </row>
     <row r="39">
@@ -1049,13 +1281,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C39" t="n">
+        <v>1.201852894853928</v>
+      </c>
+      <c r="D39" t="n">
         <v>1.171</v>
       </c>
-      <c r="D39" t="n">
-        <v>1.103337309523809</v>
+      <c r="E39" t="n">
+        <v>-0.03085289485392773</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-2.634747639105698</v>
       </c>
     </row>
     <row r="40">
@@ -1065,13 +1303,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C40" t="n">
+        <v>1.177418000552827</v>
+      </c>
+      <c r="D40" t="n">
         <v>1.198</v>
       </c>
-      <c r="D40" t="n">
-        <v>1.109357892857143</v>
+      <c r="E40" t="n">
+        <v>0.0205819994471732</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.718030003937663</v>
       </c>
     </row>
     <row r="41">
@@ -1081,13 +1325,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C41" t="n">
+        <v>1.517364903647606</v>
+      </c>
+      <c r="D41" t="n">
         <v>1.527</v>
       </c>
-      <c r="D41" t="n">
-        <v>1.538278867560801</v>
+      <c r="E41" t="n">
+        <v>0.009635096352394124</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6309820793971266</v>
       </c>
     </row>
     <row r="42">
@@ -1097,13 +1347,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C42" t="n">
+        <v>1.396763494141734</v>
+      </c>
+      <c r="D42" t="n">
         <v>1.444</v>
       </c>
-      <c r="D42" t="n">
-        <v>1.385726738972478</v>
+      <c r="E42" t="n">
+        <v>0.04723650585826555</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.271226167469913</v>
       </c>
     </row>
     <row r="43">
@@ -1113,13 +1369,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C43" t="n">
+        <v>1.345400024924749</v>
+      </c>
+      <c r="D43" t="n">
         <v>1.305</v>
       </c>
-      <c r="D43" t="n">
-        <v>1.285000035353535</v>
+      <c r="E43" t="n">
+        <v>-0.04040002492474892</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-3.095787350555473</v>
       </c>
     </row>
     <row r="44">
@@ -1129,13 +1391,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C44" t="n">
+        <v>1.299268251108358</v>
+      </c>
+      <c r="D44" t="n">
         <v>1.346</v>
       </c>
-      <c r="D44" t="n">
-        <v>1.294233996392495</v>
+      <c r="E44" t="n">
+        <v>0.04673174889164255</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.471898134594543</v>
       </c>
     </row>
     <row r="45">
@@ -1145,13 +1413,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C45" t="n">
+        <v>2.038164935635489</v>
+      </c>
+      <c r="D45" t="n">
         <v>2.03</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.039317713092462</v>
+      <c r="E45" t="n">
+        <v>-0.008164935635489368</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.4022135781029245</v>
       </c>
     </row>
     <row r="46">
@@ -1161,13 +1435,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C46" t="n">
+        <v>1.377662987036703</v>
+      </c>
+      <c r="D46" t="n">
         <v>1.414</v>
       </c>
-      <c r="D46" t="n">
-        <v>1.381564125595358</v>
+      <c r="E46" t="n">
+        <v>0.0363370129632965</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.56980289697995</v>
       </c>
     </row>
     <row r="47">
@@ -1177,13 +1457,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C47" t="n">
+        <v>1.68163562249147</v>
+      </c>
+      <c r="D47" t="n">
         <v>1.597</v>
       </c>
-      <c r="D47" t="n">
-        <v>1.634954904761904</v>
+      <c r="E47" t="n">
+        <v>-0.08463562249146994</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-5.299663274356289</v>
       </c>
     </row>
     <row r="48">
@@ -1193,13 +1479,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C48" t="n">
+        <v>1.729232724828306</v>
+      </c>
+      <c r="D48" t="n">
         <v>1.745</v>
       </c>
-      <c r="D48" t="n">
-        <v>1.738298739814925</v>
+      <c r="E48" t="n">
+        <v>0.01576727517169418</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9035687777475176</v>
       </c>
     </row>
     <row r="49">
@@ -1209,13 +1501,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C49" t="n">
+        <v>1.868862590256819</v>
+      </c>
+      <c r="D49" t="n">
         <v>1.806</v>
       </c>
-      <c r="D49" t="n">
-        <v>1.822261323023469</v>
+      <c r="E49" t="n">
+        <v>-0.0628625902568194</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-3.480763580111816</v>
       </c>
     </row>
     <row r="50">
@@ -1225,13 +1523,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C50" t="n">
+        <v>1.422157332434989</v>
+      </c>
+      <c r="D50" t="n">
         <v>1.443</v>
       </c>
-      <c r="D50" t="n">
-        <v>1.400808635215623</v>
+      <c r="E50" t="n">
+        <v>0.02084266756501107</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.444398306653574</v>
       </c>
     </row>
     <row r="51">
@@ -1241,13 +1545,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C51" t="n">
+        <v>1.51019814905425</v>
+      </c>
+      <c r="D51" t="n">
         <v>1.534</v>
       </c>
-      <c r="D51" t="n">
-        <v>1.503552709810658</v>
+      <c r="E51" t="n">
+        <v>0.02380185094574983</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.551620009501292</v>
       </c>
     </row>
     <row r="52">
@@ -1257,13 +1567,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C52" t="n">
+        <v>1.523070583203924</v>
+      </c>
+      <c r="D52" t="n">
         <v>1.564</v>
       </c>
-      <c r="D52" t="n">
-        <v>1.540493440222304</v>
+      <c r="E52" t="n">
+        <v>0.04092941679607631</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.616970383380838</v>
       </c>
     </row>
     <row r="53">
@@ -1273,13 +1589,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C53" t="n">
+        <v>1.385960603717955</v>
+      </c>
+      <c r="D53" t="n">
         <v>1.419</v>
       </c>
-      <c r="D53" t="n">
-        <v>1.389495422615816</v>
+      <c r="E53" t="n">
+        <v>0.03303939628204522</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.328357736578239</v>
       </c>
     </row>
     <row r="54">
@@ -1289,13 +1611,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C54" t="n">
+        <v>1.387545456707625</v>
+      </c>
+      <c r="D54" t="n">
         <v>1.381</v>
       </c>
-      <c r="D54" t="n">
-        <v>1.379237742780069</v>
+      <c r="E54" t="n">
+        <v>-0.006545456707624853</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.4739650041726903</v>
       </c>
     </row>
     <row r="55">
@@ -1305,13 +1633,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C55" t="n">
+        <v>1.109512121031746</v>
+      </c>
+      <c r="D55" t="n">
         <v>1.047</v>
       </c>
-      <c r="D55" t="n">
-        <v>1.062222490079364</v>
+      <c r="E55" t="n">
+        <v>-0.06251212103174608</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-5.97059417686209</v>
       </c>
     </row>
     <row r="56">
@@ -1321,13 +1655,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C56" t="n">
+        <v>1.684124487222427</v>
+      </c>
+      <c r="D56" t="n">
         <v>1.619</v>
       </c>
-      <c r="D56" t="n">
-        <v>1.656104008151795</v>
+      <c r="E56" t="n">
+        <v>-0.06512448722242747</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-4.022513108241351</v>
       </c>
     </row>
     <row r="57">
@@ -1337,13 +1677,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C57" t="n">
+        <v>1.570890382010147</v>
+      </c>
+      <c r="D57" t="n">
         <v>1.52</v>
       </c>
-      <c r="D57" t="n">
-        <v>1.548067824253304</v>
+      <c r="E57" t="n">
+        <v>-0.05089038201014695</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-3.348051448035984</v>
       </c>
     </row>
     <row r="58">
@@ -1353,13 +1699,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C58" t="n">
+        <v>1.385127971457483</v>
+      </c>
+      <c r="D58" t="n">
         <v>1.454</v>
       </c>
-      <c r="D58" t="n">
-        <v>1.407205980991923</v>
+      <c r="E58" t="n">
+        <v>0.06887202854251684</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.736728235386303</v>
       </c>
     </row>
     <row r="59">
@@ -1369,13 +1721,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C59" t="n">
+        <v>2.511203583513708</v>
+      </c>
+      <c r="D59" t="n">
         <v>2.442</v>
       </c>
-      <c r="D59" t="n">
-        <v>2.459845101731603</v>
+      <c r="E59" t="n">
+        <v>-0.06920358351370748</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-2.8338895787759</v>
       </c>
     </row>
     <row r="60">
@@ -1385,13 +1743,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C60" t="n">
+        <v>1.521519189585092</v>
+      </c>
+      <c r="D60" t="n">
         <v>1.522</v>
       </c>
-      <c r="D60" t="n">
-        <v>1.533080288554526</v>
+      <c r="E60" t="n">
+        <v>0.000480810414907662</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.03159069743151524</v>
       </c>
     </row>
     <row r="61">
@@ -1401,13 +1765,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C61" t="n">
+        <v>1.276415234610419</v>
+      </c>
+      <c r="D61" t="n">
         <v>1.272</v>
       </c>
-      <c r="D61" t="n">
-        <v>1.242127311938063</v>
+      <c r="E61" t="n">
+        <v>-0.004415234610418928</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.3471096391838779</v>
       </c>
     </row>
     <row r="62">
@@ -1417,13 +1787,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C62" t="n">
+        <v>1.160327058093466</v>
+      </c>
+      <c r="D62" t="n">
         <v>1.104</v>
       </c>
-      <c r="D62" t="n">
-        <v>1.068045865079365</v>
+      <c r="E62" t="n">
+        <v>-0.05632705809346583</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-5.102088595422629</v>
       </c>
     </row>
     <row r="63">
@@ -1433,13 +1809,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C63" t="n">
+        <v>1.318718229996038</v>
+      </c>
+      <c r="D63" t="n">
         <v>1.33</v>
       </c>
-      <c r="D63" t="n">
-        <v>1.294637494047619</v>
+      <c r="E63" t="n">
+        <v>0.01128177000396202</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.8482533837565429</v>
       </c>
     </row>
     <row r="64">
@@ -1449,13 +1831,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C64" t="n">
+        <v>1.141763421536796</v>
+      </c>
+      <c r="D64" t="n">
         <v>1.103</v>
       </c>
-      <c r="D64" t="n">
-        <v>1.060571811507936</v>
+      <c r="E64" t="n">
+        <v>-0.03876342153679624</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-3.514362786654238</v>
       </c>
     </row>
     <row r="65">
@@ -1465,13 +1853,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C65" t="n">
+        <v>1.793065015013023</v>
+      </c>
+      <c r="D65" t="n">
         <v>1.736</v>
       </c>
-      <c r="D65" t="n">
-        <v>1.729289370345157</v>
+      <c r="E65" t="n">
+        <v>-0.05706501501302252</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-3.287155242685629</v>
       </c>
     </row>
     <row r="66">
@@ -1481,13 +1875,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C66" t="n">
+        <v>1.529029945725247</v>
+      </c>
+      <c r="D66" t="n">
         <v>1.551</v>
       </c>
-      <c r="D66" t="n">
-        <v>1.546887673400674</v>
+      <c r="E66" t="n">
+        <v>0.02197005427475252</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.416508979674566</v>
       </c>
     </row>
     <row r="67">
@@ -1497,13 +1897,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C67" t="n">
+        <v>1.140438498015873</v>
+      </c>
+      <c r="D67" t="n">
         <v>1.033</v>
       </c>
-      <c r="D67" t="n">
-        <v>1.052479799603174</v>
+      <c r="E67" t="n">
+        <v>-0.1074384980158731</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-10.40062904316294</v>
       </c>
     </row>
     <row r="68">
@@ -1513,13 +1919,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C68" t="n">
+        <v>1.28057837043571</v>
+      </c>
+      <c r="D68" t="n">
         <v>1.297</v>
       </c>
-      <c r="D68" t="n">
-        <v>1.264224548049174</v>
+      <c r="E68" t="n">
+        <v>0.01642162956429027</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.266124099020068</v>
       </c>
     </row>
     <row r="69">
@@ -1529,13 +1941,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C69" t="n">
+        <v>1.197797041928118</v>
+      </c>
+      <c r="D69" t="n">
         <v>1.207</v>
       </c>
-      <c r="D69" t="n">
-        <v>1.184434231962481</v>
+      <c r="E69" t="n">
+        <v>0.009202958071881984</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.762465457488151</v>
       </c>
     </row>
     <row r="70">
@@ -1545,13 +1963,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C70" t="n">
+        <v>1.264662334903342</v>
+      </c>
+      <c r="D70" t="n">
         <v>1.278</v>
       </c>
-      <c r="D70" t="n">
-        <v>1.252879704795205</v>
+      <c r="E70" t="n">
+        <v>0.01333766509665768</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.043635766561634</v>
       </c>
     </row>
     <row r="71">
@@ -1561,13 +1985,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C71" t="n">
+        <v>1.257523725442167</v>
+      </c>
+      <c r="D71" t="n">
         <v>1.189</v>
       </c>
-      <c r="D71" t="n">
-        <v>1.17998718037518</v>
+      <c r="E71" t="n">
+        <v>-0.06852372544216734</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-5.763139229786992</v>
       </c>
     </row>
     <row r="72">
@@ -1577,13 +2007,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C72" t="n">
+        <v>1.129724173520924</v>
+      </c>
+      <c r="D72" t="n">
         <v>1.179</v>
       </c>
-      <c r="D72" t="n">
-        <v>1.087110261904762</v>
+      <c r="E72" t="n">
+        <v>0.04927582647907625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.179459412983566</v>
       </c>
     </row>
     <row r="73">
@@ -1593,13 +2029,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C73" t="n">
+        <v>1.699641264437667</v>
+      </c>
+      <c r="D73" t="n">
         <v>1.72</v>
       </c>
-      <c r="D73" t="n">
-        <v>1.707719704365359</v>
+      <c r="E73" t="n">
+        <v>0.02035873556233314</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.183647416414717</v>
       </c>
     </row>
     <row r="74">
@@ -1609,13 +2051,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C74" t="n">
+        <v>1.399175281455659</v>
+      </c>
+      <c r="D74" t="n">
         <v>1.399</v>
       </c>
-      <c r="D74" t="n">
-        <v>1.385649023327154</v>
+      <c r="E74" t="n">
+        <v>-0.0001752814556592597</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-0.01252905329944672</v>
       </c>
     </row>
     <row r="75">
@@ -1625,13 +2073,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C75" t="n">
+        <v>1.293213964165457</v>
+      </c>
+      <c r="D75" t="n">
         <v>1.34</v>
       </c>
-      <c r="D75" t="n">
-        <v>1.296922121031745</v>
+      <c r="E75" t="n">
+        <v>0.04678603583454333</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.491495211533084</v>
       </c>
     </row>
     <row r="76">
@@ -1641,29 +2095,41 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C76" t="n">
+        <v>1.50407029589413</v>
+      </c>
+      <c r="D76" t="n">
         <v>1.463</v>
       </c>
-      <c r="D76" t="n">
-        <v>1.472994753066379</v>
+      <c r="E76" t="n">
+        <v>-0.0410702958941298</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-2.807265611355421</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ - Югра</t>
+          <t>Ханты-Мансийский авт.округ-Югра</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="n">
+        <v>1.649416176064767</v>
+      </c>
+      <c r="D77" t="n">
         <v>1.659</v>
       </c>
-      <c r="D77" t="n">
-        <v>1.652842965583252</v>
+      <c r="E77" t="n">
+        <v>0.009583823935232605</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.5776867953726705</v>
       </c>
     </row>
     <row r="78">
@@ -1673,13 +2139,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C78" t="n">
+        <v>1.445753158894284</v>
+      </c>
+      <c r="D78" t="n">
         <v>1.471</v>
       </c>
-      <c r="D78" t="n">
-        <v>1.441832563492064</v>
+      <c r="E78" t="n">
+        <v>0.02524684110571562</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.716304629892292</v>
       </c>
     </row>
     <row r="79">
@@ -1689,13 +2161,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C79" t="n">
+        <v>2.487768287698413</v>
+      </c>
+      <c r="D79" t="n">
         <v>2.66</v>
       </c>
-      <c r="D79" t="n">
-        <v>2.649130948232323</v>
+      <c r="E79" t="n">
+        <v>0.1722317123015875</v>
+      </c>
+      <c r="F79" t="n">
+        <v>6.47487640231532</v>
       </c>
     </row>
     <row r="80">
@@ -1705,13 +2183,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C80" t="n">
+        <v>1.384257911436207</v>
+      </c>
+      <c r="D80" t="n">
         <v>1.402</v>
       </c>
-      <c r="D80" t="n">
-        <v>1.384772848571354</v>
+      <c r="E80" t="n">
+        <v>0.01774208856379267</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.265484205691346</v>
       </c>
     </row>
     <row r="81">
@@ -1721,13 +2205,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C81" t="n">
+        <v>1.624487659250471</v>
+      </c>
+      <c r="D81" t="n">
         <v>1.68</v>
       </c>
-      <c r="D81" t="n">
-        <v>1.651541644154681</v>
+      <c r="E81" t="n">
+        <v>0.0555123407495286</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3.30430599699575</v>
       </c>
     </row>
     <row r="82">
@@ -1737,13 +2227,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C82" t="n">
+        <v>1.894760076705123</v>
+      </c>
+      <c r="D82" t="n">
         <v>1.946</v>
       </c>
-      <c r="D82" t="n">
-        <v>1.909437232683983</v>
+      <c r="E82" t="n">
+        <v>0.05123992329487725</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.633089583498317</v>
       </c>
     </row>
     <row r="83">
@@ -1753,13 +2249,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C83" t="n">
+        <v>1.288653892202938</v>
+      </c>
+      <c r="D83" t="n">
         <v>1.316</v>
       </c>
-      <c r="D83" t="n">
-        <v>1.280010443070819</v>
+      <c r="E83" t="n">
+        <v>0.02734610779706159</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.077971717101944</v>
       </c>
     </row>
     <row r="84">
@@ -1769,13 +2271,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C84" t="n">
+        <v>1.389753904440746</v>
+      </c>
+      <c r="D84" t="n">
         <v>1.424</v>
       </c>
-      <c r="D84" t="n">
-        <v>1.401762851406135</v>
+      <c r="E84" t="n">
+        <v>0.03424609555925362</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.404922440958822</v>
       </c>
     </row>
     <row r="85">
@@ -1785,13 +2293,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C85" t="n">
+        <v>1.292269705452077</v>
+      </c>
+      <c r="D85" t="n">
         <v>1.257</v>
       </c>
-      <c r="D85" t="n">
-        <v>1.248971165112666</v>
+      <c r="E85" t="n">
+        <v>-0.03526970545207719</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-2.805863600006141</v>
       </c>
     </row>
     <row r="86">
@@ -1801,13 +2315,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C86" t="n">
+        <v>1.138718121031746</v>
+      </c>
+      <c r="D86" t="n">
         <v>0.976</v>
       </c>
-      <c r="D86" t="n">
-        <v>1.061944382936507</v>
+      <c r="E86" t="n">
+        <v>-0.1627181210317459</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-16.67193863030183</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/Random Forest/predictions_afr.xlsx
+++ b/notebooks/Random Forest/predictions_afr.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>СКР_реальный</t>
+          <t>СКР</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -498,10 +498,10 @@
         <v>1.49</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04877464983502477</v>
+        <v>0.04877464983502455</v>
       </c>
       <c r="F3" t="n">
-        <v>3.273466431880857</v>
+        <v>3.273466431880843</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>1.459</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01776336404875845</v>
+        <v>-0.01776336404875867</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.217502676405651</v>
+        <v>-1.217502676405666</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>1.635</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02955183900199754</v>
+        <v>0.02955183900199776</v>
       </c>
       <c r="F5" t="n">
-        <v>1.807451926727678</v>
+        <v>1.807451926727692</v>
       </c>
     </row>
     <row r="6">
@@ -608,10 +608,10 @@
         <v>1.147</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01259951517246627</v>
+        <v>-0.01259951517246605</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.098475603528009</v>
+        <v>-1.09847560352799</v>
       </c>
     </row>
     <row r="9">
@@ -646,16 +646,16 @@
         <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>1.374991444656341</v>
+        <v>1.374991444656342</v>
       </c>
       <c r="D10" t="n">
         <v>1.391</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01600855534365864</v>
+        <v>0.01600855534365819</v>
       </c>
       <c r="F10" t="n">
-        <v>1.15086666740896</v>
+        <v>1.150866667408928</v>
       </c>
     </row>
     <row r="11">
@@ -674,10 +674,10 @@
         <v>1.222</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0004657119357081019</v>
+        <v>0.0004657119357083239</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03811063303666955</v>
+        <v>0.03811063303668772</v>
       </c>
     </row>
     <row r="12">
@@ -696,10 +696,10 @@
         <v>1.559</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04299600355382771</v>
+        <v>-0.04299600355382793</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.75792197266374</v>
+        <v>-2.757921972663755</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         <v>2023</v>
       </c>
       <c r="C13" t="n">
-        <v>1.609771294701715</v>
+        <v>1.609771294701716</v>
       </c>
       <c r="D13" t="n">
         <v>1.548</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06177129470171505</v>
+        <v>-0.06177129470171594</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.990393714581075</v>
+        <v>-3.990393714581133</v>
       </c>
     </row>
     <row r="14">
@@ -740,10 +740,10 @@
         <v>1.346</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.008218973423503417</v>
+        <v>-0.008218973423503861</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6106220968427502</v>
+        <v>-0.6106220968427831</v>
       </c>
     </row>
     <row r="15">
@@ -762,10 +762,10 @@
         <v>1.65</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01548395713544704</v>
+        <v>-0.01548395713544748</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9384216445725476</v>
+        <v>-0.9384216445725745</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         <v>2023</v>
       </c>
       <c r="C16" t="n">
-        <v>1.522749674501962</v>
+        <v>1.522749674501963</v>
       </c>
       <c r="D16" t="n">
         <v>1.526</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00325032549803761</v>
+        <v>0.003250325498037387</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2129964284428315</v>
+        <v>0.212996428442817</v>
       </c>
     </row>
     <row r="17">
@@ -806,10 +806,10 @@
         <v>1.183</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1060726222325112</v>
+        <v>-0.106072622232511</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.966409318048287</v>
+        <v>-8.966409318048269</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         <v>2023</v>
       </c>
       <c r="C18" t="n">
-        <v>1.316430579274658</v>
+        <v>1.316430579274659</v>
       </c>
       <c r="D18" t="n">
         <v>1.339</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02256942072534174</v>
+        <v>0.02256942072534085</v>
       </c>
       <c r="F18" t="n">
-        <v>1.685542996664805</v>
+        <v>1.685542996664739</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         <v>2023</v>
       </c>
       <c r="C19" t="n">
-        <v>1.601448499936831</v>
+        <v>1.601448499936832</v>
       </c>
       <c r="D19" t="n">
         <v>1.666</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06455150006316868</v>
+        <v>0.06455150006316757</v>
       </c>
       <c r="F19" t="n">
-        <v>3.874639859734014</v>
+        <v>3.874639859733948</v>
       </c>
     </row>
     <row r="20">
@@ -872,10 +872,10 @@
         <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008131551871902065</v>
+        <v>0.008131551871902509</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6068322292464228</v>
+        <v>0.6068322292464559</v>
       </c>
     </row>
     <row r="21">
@@ -910,16 +910,16 @@
         <v>2023</v>
       </c>
       <c r="C22" t="n">
-        <v>1.48281620002669</v>
+        <v>1.482816200026691</v>
       </c>
       <c r="D22" t="n">
         <v>1.473</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.009816200026689925</v>
+        <v>-0.009816200026690813</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6664086915607552</v>
+        <v>-0.6664086915608156</v>
       </c>
     </row>
     <row r="23">
@@ -938,10 +938,10 @@
         <v>1.552</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05834009247378402</v>
+        <v>0.0583400924737838</v>
       </c>
       <c r="F23" t="n">
-        <v>3.759026576919074</v>
+        <v>3.759026576919059</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         <v>2023</v>
       </c>
       <c r="C24" t="n">
-        <v>1.503597848628165</v>
+        <v>1.503597848628164</v>
       </c>
       <c r="D24" t="n">
         <v>1.532</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0284021513718351</v>
+        <v>0.02840215137183555</v>
       </c>
       <c r="F24" t="n">
-        <v>1.85392632975425</v>
+        <v>1.853926329754279</v>
       </c>
     </row>
     <row r="25">
@@ -982,10 +982,10 @@
         <v>1.436</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02885766630018871</v>
+        <v>0.02885766630018849</v>
       </c>
       <c r="F25" t="n">
-        <v>2.009586789706735</v>
+        <v>2.00958678970672</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         <v>2023</v>
       </c>
       <c r="C26" t="n">
-        <v>1.649311918951633</v>
+        <v>1.649311918951634</v>
       </c>
       <c r="D26" t="n">
         <v>1.642</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.007311918951633523</v>
+        <v>-0.007311918951633967</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4453056608790208</v>
+        <v>-0.4453056608790479</v>
       </c>
     </row>
     <row r="27">
@@ -1070,10 +1070,10 @@
         <v>1.233</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03041458248621121</v>
+        <v>0.03041458248621076</v>
       </c>
       <c r="F29" t="n">
-        <v>2.466713908046326</v>
+        <v>2.46671390804629</v>
       </c>
     </row>
     <row r="30">
@@ -1114,10 +1114,10 @@
         <v>1.352</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04735352843915375</v>
+        <v>0.04735352843915419</v>
       </c>
       <c r="F31" t="n">
-        <v>3.502479914138591</v>
+        <v>3.502479914138623</v>
       </c>
     </row>
     <row r="32">
@@ -1136,10 +1136,10 @@
         <v>1.451</v>
       </c>
       <c r="E32" t="n">
-        <v>0.008014453002607835</v>
+        <v>0.008014453002607613</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5523399726125316</v>
+        <v>0.5523399726125164</v>
       </c>
     </row>
     <row r="33">
@@ -1180,10 +1180,10 @@
         <v>1.309</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0176064560648812</v>
+        <v>0.01760645606488098</v>
       </c>
       <c r="F34" t="n">
-        <v>1.345031020999328</v>
+        <v>1.345031020999311</v>
       </c>
     </row>
     <row r="35">
@@ -1218,16 +1218,16 @@
         <v>2023</v>
       </c>
       <c r="C36" t="n">
-        <v>1.485267188353305</v>
+        <v>1.485267188353306</v>
       </c>
       <c r="D36" t="n">
         <v>1.492</v>
       </c>
       <c r="E36" t="n">
-        <v>0.006732811646695147</v>
+        <v>0.006732811646694481</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4512608342288973</v>
+        <v>0.4512608342288526</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         <v>2023</v>
       </c>
       <c r="C37" t="n">
-        <v>1.497830622332682</v>
+        <v>1.497830622332683</v>
       </c>
       <c r="D37" t="n">
         <v>1.495</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.002830622332682386</v>
+        <v>-0.002830622332682609</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1893392864670493</v>
+        <v>-0.1893392864670641</v>
       </c>
     </row>
     <row r="38">
@@ -1268,10 +1268,10 @@
         <v>1.502</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0424397556399565</v>
+        <v>0.04243975563995561</v>
       </c>
       <c r="F38" t="n">
-        <v>2.825549643139581</v>
+        <v>2.825549643139521</v>
       </c>
     </row>
     <row r="39">
@@ -1334,10 +1334,10 @@
         <v>1.527</v>
       </c>
       <c r="E41" t="n">
-        <v>0.009635096352394124</v>
+        <v>0.009635096352393679</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6309820793971266</v>
+        <v>0.6309820793970976</v>
       </c>
     </row>
     <row r="42">
@@ -1356,10 +1356,10 @@
         <v>1.444</v>
       </c>
       <c r="E42" t="n">
-        <v>0.04723650585826555</v>
+        <v>0.04723650585826578</v>
       </c>
       <c r="F42" t="n">
-        <v>3.271226167469913</v>
+        <v>3.271226167469929</v>
       </c>
     </row>
     <row r="43">
@@ -1378,10 +1378,10 @@
         <v>1.305</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.04040002492474892</v>
+        <v>-0.0404000249247487</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.095787350555473</v>
+        <v>-3.095787350555456</v>
       </c>
     </row>
     <row r="44">
@@ -1438,16 +1438,16 @@
         <v>2023</v>
       </c>
       <c r="C46" t="n">
-        <v>1.377662987036703</v>
+        <v>1.377662987036704</v>
       </c>
       <c r="D46" t="n">
         <v>1.414</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0363370129632965</v>
+        <v>0.03633701296329561</v>
       </c>
       <c r="F46" t="n">
-        <v>2.56980289697995</v>
+        <v>2.569802896979888</v>
       </c>
     </row>
     <row r="47">
@@ -1482,16 +1482,16 @@
         <v>2023</v>
       </c>
       <c r="C48" t="n">
-        <v>1.729232724828306</v>
+        <v>1.729232724828307</v>
       </c>
       <c r="D48" t="n">
         <v>1.745</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01576727517169418</v>
+        <v>0.01576727517169352</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9035687777475176</v>
+        <v>0.9035687777474796</v>
       </c>
     </row>
     <row r="49">
@@ -1554,10 +1554,10 @@
         <v>1.534</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02380185094574983</v>
+        <v>0.0238018509457496</v>
       </c>
       <c r="F51" t="n">
-        <v>1.551620009501292</v>
+        <v>1.551620009501278</v>
       </c>
     </row>
     <row r="52">
@@ -1598,10 +1598,10 @@
         <v>1.419</v>
       </c>
       <c r="E53" t="n">
-        <v>0.03303939628204522</v>
+        <v>0.03303939628204478</v>
       </c>
       <c r="F53" t="n">
-        <v>2.328357736578239</v>
+        <v>2.328357736578208</v>
       </c>
     </row>
     <row r="54">
@@ -1614,16 +1614,16 @@
         <v>2023</v>
       </c>
       <c r="C54" t="n">
-        <v>1.387545456707625</v>
+        <v>1.387545456707626</v>
       </c>
       <c r="D54" t="n">
         <v>1.381</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.006545456707624853</v>
+        <v>-0.006545456707625519</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4739650041726903</v>
+        <v>-0.4739650041727385</v>
       </c>
     </row>
     <row r="55">
@@ -1642,10 +1642,10 @@
         <v>1.047</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.06251212103174608</v>
+        <v>-0.06251212103174586</v>
       </c>
       <c r="F55" t="n">
-        <v>-5.97059417686209</v>
+        <v>-5.970594176862069</v>
       </c>
     </row>
     <row r="56">
@@ -1708,10 +1708,10 @@
         <v>1.454</v>
       </c>
       <c r="E58" t="n">
-        <v>0.06887202854251684</v>
+        <v>0.06887202854251706</v>
       </c>
       <c r="F58" t="n">
-        <v>4.736728235386303</v>
+        <v>4.736728235386318</v>
       </c>
     </row>
     <row r="59">
@@ -1746,16 +1746,16 @@
         <v>2023</v>
       </c>
       <c r="C60" t="n">
-        <v>1.521519189585092</v>
+        <v>1.521519189585093</v>
       </c>
       <c r="D60" t="n">
         <v>1.522</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000480810414907662</v>
+        <v>0.0004808104149072179</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03159069743151524</v>
+        <v>0.03159069743148606</v>
       </c>
     </row>
     <row r="61">
@@ -1774,10 +1774,10 @@
         <v>1.272</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.004415234610418928</v>
+        <v>-0.004415234610418706</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3471096391838779</v>
+        <v>-0.3471096391838605</v>
       </c>
     </row>
     <row r="62">
@@ -1796,10 +1796,10 @@
         <v>1.104</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.05632705809346583</v>
+        <v>-0.05632705809346605</v>
       </c>
       <c r="F62" t="n">
-        <v>-5.102088595422629</v>
+        <v>-5.102088595422649</v>
       </c>
     </row>
     <row r="63">
@@ -1818,10 +1818,10 @@
         <v>1.33</v>
       </c>
       <c r="E63" t="n">
-        <v>0.01128177000396202</v>
+        <v>0.0112817700039618</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8482533837565429</v>
+        <v>0.8482533837565263</v>
       </c>
     </row>
     <row r="64">
@@ -1862,10 +1862,10 @@
         <v>1.736</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.05706501501302252</v>
+        <v>-0.05706501501302319</v>
       </c>
       <c r="F65" t="n">
-        <v>-3.287155242685629</v>
+        <v>-3.287155242685667</v>
       </c>
     </row>
     <row r="66">
@@ -1884,10 +1884,10 @@
         <v>1.551</v>
       </c>
       <c r="E66" t="n">
-        <v>0.02197005427475252</v>
+        <v>0.02197005427475296</v>
       </c>
       <c r="F66" t="n">
-        <v>1.416508979674566</v>
+        <v>1.416508979674594</v>
       </c>
     </row>
     <row r="67">
@@ -1906,10 +1906,10 @@
         <v>1.033</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.1074384980158731</v>
+        <v>-0.1074384980158734</v>
       </c>
       <c r="F67" t="n">
-        <v>-10.40062904316294</v>
+        <v>-10.40062904316296</v>
       </c>
     </row>
     <row r="68">
@@ -1922,16 +1922,16 @@
         <v>2023</v>
       </c>
       <c r="C68" t="n">
-        <v>1.28057837043571</v>
+        <v>1.280578370435709</v>
       </c>
       <c r="D68" t="n">
         <v>1.297</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01642162956429027</v>
+        <v>0.0164216295642905</v>
       </c>
       <c r="F68" t="n">
-        <v>1.266124099020068</v>
+        <v>1.266124099020085</v>
       </c>
     </row>
     <row r="69">
@@ -1972,10 +1972,10 @@
         <v>1.278</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01333766509665768</v>
+        <v>0.0133376650966579</v>
       </c>
       <c r="F70" t="n">
-        <v>1.043635766561634</v>
+        <v>1.043635766561651</v>
       </c>
     </row>
     <row r="71">
@@ -1994,10 +1994,10 @@
         <v>1.189</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.06852372544216734</v>
+        <v>-0.06852372544216712</v>
       </c>
       <c r="F71" t="n">
-        <v>-5.763139229786992</v>
+        <v>-5.763139229786973</v>
       </c>
     </row>
     <row r="72">
@@ -2038,10 +2038,10 @@
         <v>1.72</v>
       </c>
       <c r="E73" t="n">
-        <v>0.02035873556233314</v>
+        <v>0.0203587355623327</v>
       </c>
       <c r="F73" t="n">
-        <v>1.183647416414717</v>
+        <v>1.183647416414692</v>
       </c>
     </row>
     <row r="74">
@@ -2054,16 +2054,16 @@
         <v>2023</v>
       </c>
       <c r="C74" t="n">
-        <v>1.399175281455659</v>
+        <v>1.39917528145566</v>
       </c>
       <c r="D74" t="n">
         <v>1.399</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.0001752814556592597</v>
+        <v>-0.0001752814556597038</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.01252905329944672</v>
+        <v>-0.01252905329947847</v>
       </c>
     </row>
     <row r="75">
@@ -2076,16 +2076,16 @@
         <v>2023</v>
       </c>
       <c r="C75" t="n">
-        <v>1.293213964165457</v>
+        <v>1.293213964165456</v>
       </c>
       <c r="D75" t="n">
         <v>1.34</v>
       </c>
       <c r="E75" t="n">
-        <v>0.04678603583454333</v>
+        <v>0.04678603583454377</v>
       </c>
       <c r="F75" t="n">
-        <v>3.491495211533084</v>
+        <v>3.491495211533117</v>
       </c>
     </row>
     <row r="76">
@@ -2104,10 +2104,10 @@
         <v>1.463</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.0410702958941298</v>
+        <v>-0.04107029589413003</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.807265611355421</v>
+        <v>-2.807265611355436</v>
       </c>
     </row>
     <row r="77">
@@ -2126,10 +2126,10 @@
         <v>1.659</v>
       </c>
       <c r="E77" t="n">
-        <v>0.009583823935232605</v>
+        <v>0.009583823935233271</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5776867953726705</v>
+        <v>0.5776867953727107</v>
       </c>
     </row>
     <row r="78">
@@ -2142,16 +2142,16 @@
         <v>2023</v>
       </c>
       <c r="C78" t="n">
-        <v>1.445753158894284</v>
+        <v>1.445753158894285</v>
       </c>
       <c r="D78" t="n">
         <v>1.471</v>
       </c>
       <c r="E78" t="n">
-        <v>0.02524684110571562</v>
+        <v>0.02524684110571496</v>
       </c>
       <c r="F78" t="n">
-        <v>1.716304629892292</v>
+        <v>1.716304629892247</v>
       </c>
     </row>
     <row r="79">
@@ -2192,10 +2192,10 @@
         <v>1.402</v>
       </c>
       <c r="E80" t="n">
-        <v>0.01774208856379267</v>
+        <v>0.01774208856379245</v>
       </c>
       <c r="F80" t="n">
-        <v>1.265484205691346</v>
+        <v>1.26548420569133</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>1.624487659250471</v>
+        <v>1.624487659250472</v>
       </c>
       <c r="D81" t="n">
         <v>1.68</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0555123407495286</v>
+        <v>0.05551234074952816</v>
       </c>
       <c r="F81" t="n">
-        <v>3.30430599699575</v>
+        <v>3.304305996995724</v>
       </c>
     </row>
     <row r="82">
@@ -2230,16 +2230,16 @@
         <v>2023</v>
       </c>
       <c r="C82" t="n">
-        <v>1.894760076705123</v>
+        <v>1.894760076705122</v>
       </c>
       <c r="D82" t="n">
         <v>1.946</v>
       </c>
       <c r="E82" t="n">
-        <v>0.05123992329487725</v>
+        <v>0.05123992329487748</v>
       </c>
       <c r="F82" t="n">
-        <v>2.633089583498317</v>
+        <v>2.633089583498329</v>
       </c>
     </row>
     <row r="83">
@@ -2252,16 +2252,16 @@
         <v>2023</v>
       </c>
       <c r="C83" t="n">
-        <v>1.288653892202938</v>
+        <v>1.288653892202939</v>
       </c>
       <c r="D83" t="n">
         <v>1.316</v>
       </c>
       <c r="E83" t="n">
-        <v>0.02734610779706159</v>
+        <v>0.02734610779706137</v>
       </c>
       <c r="F83" t="n">
-        <v>2.077971717101944</v>
+        <v>2.077971717101928</v>
       </c>
     </row>
     <row r="84">
